--- a/Team-Data/2012-13/4-9-2012-13.xlsx
+++ b/Team-Data/2012-13/4-9-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>0.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE2" t="n">
         <v>12</v>
@@ -751,7 +818,7 @@
         <v>13</v>
       </c>
       <c r="AH2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI2" t="n">
         <v>12</v>
@@ -769,7 +836,7 @@
         <v>5</v>
       </c>
       <c r="AN2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO2" t="n">
         <v>28</v>
@@ -793,7 +860,7 @@
         <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW2" t="n">
         <v>14</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-9-2012-13</t>
+          <t>2013-04-09</t>
         </is>
       </c>
     </row>
@@ -921,10 +988,10 @@
         <v>-0.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="AE3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF3" t="n">
         <v>14</v>
@@ -939,7 +1006,7 @@
         <v>17</v>
       </c>
       <c r="AJ3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK3" t="n">
         <v>7</v>
@@ -951,10 +1018,10 @@
         <v>26</v>
       </c>
       <c r="AN3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP3" t="n">
         <v>19</v>
@@ -990,13 +1057,13 @@
         <v>27</v>
       </c>
       <c r="BA3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB3" t="n">
         <v>19</v>
       </c>
       <c r="BC3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-9-2012-13</t>
+          <t>2013-04-09</t>
         </is>
       </c>
     </row>
@@ -1025,28 +1092,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E4" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F4" t="n">
         <v>32</v>
       </c>
       <c r="G4" t="n">
-        <v>0.584</v>
+        <v>0.579</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
       </c>
       <c r="I4" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="J4" t="n">
-        <v>79.59999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L4" t="n">
         <v>7.6</v>
@@ -1055,7 +1122,7 @@
         <v>21.4</v>
       </c>
       <c r="N4" t="n">
-        <v>0.355</v>
+        <v>0.356</v>
       </c>
       <c r="O4" t="n">
         <v>17.5</v>
@@ -1064,22 +1131,22 @@
         <v>23.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.733</v>
+        <v>0.734</v>
       </c>
       <c r="R4" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="S4" t="n">
-        <v>30.2</v>
+        <v>30</v>
       </c>
       <c r="T4" t="n">
-        <v>43</v>
+        <v>42.6</v>
       </c>
       <c r="U4" t="n">
         <v>20.3</v>
       </c>
       <c r="V4" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W4" t="n">
         <v>7.1</v>
@@ -1094,16 +1161,16 @@
         <v>18.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>96.5</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="AE4" t="n">
         <v>9</v>
@@ -1121,10 +1188,10 @@
         <v>26</v>
       </c>
       <c r="AJ4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL4" t="n">
         <v>9</v>
@@ -1133,10 +1200,10 @@
         <v>8</v>
       </c>
       <c r="AN4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AO4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP4" t="n">
         <v>7</v>
@@ -1145,10 +1212,10 @@
         <v>24</v>
       </c>
       <c r="AR4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AT4" t="n">
         <v>10</v>
@@ -1157,10 +1224,10 @@
         <v>28</v>
       </c>
       <c r="AV4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX4" t="n">
         <v>17</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-9-2012-13</t>
+          <t>2013-04-09</t>
         </is>
       </c>
     </row>
@@ -1207,43 +1274,43 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E5" t="n">
         <v>18</v>
       </c>
       <c r="F5" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G5" t="n">
-        <v>0.231</v>
+        <v>0.234</v>
       </c>
       <c r="H5" t="n">
         <v>48.3</v>
       </c>
       <c r="I5" t="n">
-        <v>34.2</v>
+        <v>34.3</v>
       </c>
       <c r="J5" t="n">
-        <v>81.3</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.421</v>
+        <v>0.422</v>
       </c>
       <c r="L5" t="n">
         <v>5.7</v>
       </c>
       <c r="M5" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="N5" t="n">
-        <v>0.332</v>
+        <v>0.334</v>
       </c>
       <c r="O5" t="n">
         <v>19</v>
       </c>
       <c r="P5" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="Q5" t="n">
         <v>0.749</v>
@@ -1258,13 +1325,13 @@
         <v>40.3</v>
       </c>
       <c r="U5" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="V5" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W5" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X5" t="n">
         <v>5.9</v>
@@ -1279,19 +1346,19 @@
         <v>21.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>93.09999999999999</v>
+        <v>93.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>-9.800000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE5" t="n">
         <v>30</v>
       </c>
       <c r="AF5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG5" t="n">
         <v>30</v>
@@ -1309,16 +1376,16 @@
         <v>30</v>
       </c>
       <c r="AL5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AM5" t="n">
         <v>27</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>28</v>
       </c>
       <c r="AN5" t="n">
         <v>27</v>
       </c>
       <c r="AO5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP5" t="n">
         <v>5</v>
@@ -1357,7 +1424,7 @@
         <v>5</v>
       </c>
       <c r="BB5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC5" t="n">
         <v>30</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-9-2012-13</t>
+          <t>2013-04-09</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E6" t="n">
         <v>42</v>
       </c>
       <c r="F6" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G6" t="n">
-        <v>0.545</v>
+        <v>0.553</v>
       </c>
       <c r="H6" t="n">
         <v>48.3</v>
@@ -1413,13 +1480,13 @@
         <v>0.436</v>
       </c>
       <c r="L6" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="M6" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="N6" t="n">
-        <v>0.345</v>
+        <v>0.342</v>
       </c>
       <c r="O6" t="n">
         <v>16.3</v>
@@ -1428,7 +1495,7 @@
         <v>21.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.773</v>
+        <v>0.774</v>
       </c>
       <c r="R6" t="n">
         <v>12.7</v>
@@ -1446,7 +1513,7 @@
         <v>14.3</v>
       </c>
       <c r="W6" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X6" t="n">
         <v>5.2</v>
@@ -1461,19 +1528,19 @@
         <v>19.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>92.8</v>
+        <v>92.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="AE6" t="n">
         <v>12</v>
       </c>
       <c r="AF6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG6" t="n">
         <v>12</v>
@@ -1482,10 +1549,10 @@
         <v>15</v>
       </c>
       <c r="AI6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK6" t="n">
         <v>26</v>
@@ -1497,10 +1564,10 @@
         <v>29</v>
       </c>
       <c r="AN6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP6" t="n">
         <v>22</v>
@@ -1509,7 +1576,7 @@
         <v>10</v>
       </c>
       <c r="AR6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS6" t="n">
         <v>14</v>
@@ -1527,7 +1594,7 @@
         <v>20</v>
       </c>
       <c r="AX6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY6" t="n">
         <v>22</v>
@@ -1536,10 +1603,10 @@
         <v>11</v>
       </c>
       <c r="BA6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC6" t="n">
         <v>14</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-9-2012-13</t>
+          <t>2013-04-09</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E7" t="n">
         <v>24</v>
       </c>
       <c r="F7" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G7" t="n">
-        <v>0.312</v>
+        <v>0.316</v>
       </c>
       <c r="H7" t="n">
         <v>48.1</v>
@@ -1598,7 +1665,7 @@
         <v>6.8</v>
       </c>
       <c r="M7" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="N7" t="n">
         <v>0.349</v>
@@ -1607,10 +1674,10 @@
         <v>17</v>
       </c>
       <c r="P7" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.759</v>
+        <v>0.758</v>
       </c>
       <c r="R7" t="n">
         <v>12.3</v>
@@ -1622,7 +1689,7 @@
         <v>40.9</v>
       </c>
       <c r="U7" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="V7" t="n">
         <v>14.1</v>
@@ -1637,25 +1704,25 @@
         <v>6.9</v>
       </c>
       <c r="Z7" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AA7" t="n">
         <v>19.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>96.7</v>
+        <v>96.8</v>
       </c>
       <c r="AC7" t="n">
         <v>-4.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="AE7" t="n">
         <v>27</v>
       </c>
       <c r="AF7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG7" t="n">
         <v>27</v>
@@ -1691,7 +1758,7 @@
         <v>16</v>
       </c>
       <c r="AR7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS7" t="n">
         <v>30</v>
@@ -1703,10 +1770,10 @@
         <v>25</v>
       </c>
       <c r="AV7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX7" t="n">
         <v>29</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-9-2012-13</t>
+          <t>2013-04-09</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>-0.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="AE8" t="n">
         <v>17</v>
@@ -1861,10 +1928,10 @@
         <v>12</v>
       </c>
       <c r="AN8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP8" t="n">
         <v>25</v>
@@ -1885,7 +1952,7 @@
         <v>6</v>
       </c>
       <c r="AV8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW8" t="n">
         <v>17</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-9-2012-13</t>
+          <t>2013-04-09</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>4.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="AE9" t="n">
         <v>4</v>
@@ -2025,7 +2092,7 @@
         <v>4</v>
       </c>
       <c r="AH9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI9" t="n">
         <v>1</v>
@@ -2043,7 +2110,7 @@
         <v>19</v>
       </c>
       <c r="AN9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO9" t="n">
         <v>6</v>
@@ -2061,13 +2128,13 @@
         <v>11</v>
       </c>
       <c r="AT9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU9" t="n">
         <v>3</v>
       </c>
       <c r="AV9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW9" t="n">
         <v>2</v>
@@ -2079,13 +2146,13 @@
         <v>28</v>
       </c>
       <c r="AZ9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC9" t="n">
         <v>5</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-9-2012-13</t>
+          <t>2013-04-09</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-4.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
         <v>26</v>
@@ -2207,7 +2274,7 @@
         <v>26</v>
       </c>
       <c r="AH10" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AI10" t="n">
         <v>23</v>
@@ -2225,7 +2292,7 @@
         <v>23</v>
       </c>
       <c r="AN10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO10" t="n">
         <v>23</v>
@@ -2240,7 +2307,7 @@
         <v>9</v>
       </c>
       <c r="AS10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT10" t="n">
         <v>14</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-9-2012-13</t>
+          <t>2013-04-09</t>
         </is>
       </c>
     </row>
@@ -2299,37 +2366,37 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E11" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F11" t="n">
         <v>33</v>
       </c>
       <c r="G11" t="n">
-        <v>0.577</v>
+        <v>0.571</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="J11" t="n">
-        <v>83.09999999999999</v>
+        <v>83</v>
       </c>
       <c r="K11" t="n">
         <v>0.457</v>
       </c>
       <c r="L11" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="M11" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0.402</v>
+        <v>0.401</v>
       </c>
       <c r="O11" t="n">
         <v>17</v>
@@ -2338,16 +2405,16 @@
         <v>21.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.792</v>
+        <v>0.793</v>
       </c>
       <c r="R11" t="n">
         <v>10.8</v>
       </c>
       <c r="S11" t="n">
-        <v>34.1</v>
+        <v>33.9</v>
       </c>
       <c r="T11" t="n">
-        <v>44.8</v>
+        <v>44.6</v>
       </c>
       <c r="U11" t="n">
         <v>22.5</v>
@@ -2371,13 +2438,13 @@
         <v>19.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>100.9</v>
+        <v>100.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE11" t="n">
         <v>9</v>
@@ -2425,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="AT11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AU11" t="n">
         <v>14</v>
@@ -2434,19 +2501,19 @@
         <v>27</v>
       </c>
       <c r="AW11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX11" t="n">
         <v>26</v>
       </c>
       <c r="AY11" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ11" t="n">
         <v>28</v>
       </c>
       <c r="BA11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB11" t="n">
         <v>9</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-9-2012-13</t>
+          <t>2013-04-09</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E12" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F12" t="n">
         <v>34</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="H12" t="n">
         <v>48.2</v>
@@ -2499,7 +2566,7 @@
         <v>38.2</v>
       </c>
       <c r="J12" t="n">
-        <v>82.7</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K12" t="n">
         <v>0.462</v>
@@ -2511,19 +2578,19 @@
         <v>28.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0.367</v>
+        <v>0.369</v>
       </c>
       <c r="O12" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="P12" t="n">
         <v>25.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.756</v>
+        <v>0.754</v>
       </c>
       <c r="R12" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="S12" t="n">
         <v>32.1</v>
@@ -2538,19 +2605,19 @@
         <v>16.4</v>
       </c>
       <c r="W12" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y12" t="n">
         <v>6</v>
       </c>
       <c r="Z12" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB12" t="n">
         <v>106.2</v>
@@ -2559,7 +2626,7 @@
         <v>3.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE12" t="n">
         <v>11</v>
@@ -2574,7 +2641,7 @@
         <v>24</v>
       </c>
       <c r="AI12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ12" t="n">
         <v>10</v>
@@ -2586,10 +2653,10 @@
         <v>2</v>
       </c>
       <c r="AM12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO12" t="n">
         <v>2</v>
@@ -2616,7 +2683,7 @@
         <v>30</v>
       </c>
       <c r="AW12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX12" t="n">
         <v>27</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-9-2012-13</t>
+          <t>2013-04-09</t>
         </is>
       </c>
     </row>
@@ -2663,22 +2730,22 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E13" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F13" t="n">
         <v>29</v>
       </c>
       <c r="G13" t="n">
-        <v>0.628</v>
+        <v>0.623</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
       </c>
       <c r="I13" t="n">
-        <v>35.1</v>
+        <v>35.2</v>
       </c>
       <c r="J13" t="n">
         <v>80.8</v>
@@ -2687,25 +2754,25 @@
         <v>0.435</v>
       </c>
       <c r="L13" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="M13" t="n">
         <v>19.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0.349</v>
+        <v>0.35</v>
       </c>
       <c r="O13" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="P13" t="n">
-        <v>23.5</v>
+        <v>23.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.749</v>
+        <v>0.751</v>
       </c>
       <c r="R13" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="S13" t="n">
         <v>33.2</v>
@@ -2714,7 +2781,7 @@
         <v>46.1</v>
       </c>
       <c r="U13" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="V13" t="n">
         <v>15</v>
@@ -2729,10 +2796,10 @@
         <v>5.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="AB13" t="n">
         <v>94.7</v>
@@ -2741,7 +2808,7 @@
         <v>4.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE13" t="n">
         <v>8</v>
@@ -2753,7 +2820,7 @@
         <v>8</v>
       </c>
       <c r="AH13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI13" t="n">
         <v>29</v>
@@ -2774,19 +2841,19 @@
         <v>21</v>
       </c>
       <c r="AO13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AP13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ13" t="n">
         <v>18</v>
       </c>
       <c r="AR13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT13" t="n">
         <v>1</v>
@@ -2795,10 +2862,10 @@
         <v>27</v>
       </c>
       <c r="AV13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW13" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AX13" t="n">
         <v>4</v>
@@ -2807,10 +2874,10 @@
         <v>20</v>
       </c>
       <c r="AZ13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB13" t="n">
         <v>22</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-9-2012-13</t>
+          <t>2013-04-09</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>6.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="AE14" t="n">
         <v>6</v>
@@ -2935,7 +3002,7 @@
         <v>6</v>
       </c>
       <c r="AH14" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AI14" t="n">
         <v>5</v>
@@ -2959,7 +3026,7 @@
         <v>16</v>
       </c>
       <c r="AP14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ14" t="n">
         <v>26</v>
@@ -2971,7 +3038,7 @@
         <v>21</v>
       </c>
       <c r="AT14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU14" t="n">
         <v>4</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-9-2012-13</t>
+          <t>2013-04-09</t>
         </is>
       </c>
     </row>
@@ -3027,22 +3094,22 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E15" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F15" t="n">
         <v>37</v>
       </c>
       <c r="G15" t="n">
-        <v>0.526</v>
+        <v>0.519</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
       </c>
       <c r="I15" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J15" t="n">
         <v>81.09999999999999</v>
@@ -3057,7 +3124,7 @@
         <v>24.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0.355</v>
+        <v>0.356</v>
       </c>
       <c r="O15" t="n">
         <v>19</v>
@@ -3066,10 +3133,10 @@
         <v>27.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S15" t="n">
         <v>33.1</v>
@@ -3096,34 +3163,34 @@
         <v>18</v>
       </c>
       <c r="AA15" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>102.1</v>
+        <v>102</v>
       </c>
       <c r="AC15" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF15" t="n">
         <v>14</v>
       </c>
       <c r="AG15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AJ15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK15" t="n">
         <v>10</v>
@@ -3138,7 +3205,7 @@
         <v>19</v>
       </c>
       <c r="AO15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP15" t="n">
         <v>1</v>
@@ -3153,22 +3220,22 @@
         <v>5</v>
       </c>
       <c r="AT15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU15" t="n">
         <v>17</v>
       </c>
       <c r="AV15" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AW15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX15" t="n">
         <v>15</v>
       </c>
       <c r="AY15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ15" t="n">
         <v>2</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-9-2012-13</t>
+          <t>2013-04-09</t>
         </is>
       </c>
     </row>
@@ -3209,28 +3276,28 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F16" t="n">
         <v>25</v>
       </c>
       <c r="G16" t="n">
-        <v>0.679</v>
+        <v>0.675</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
       </c>
       <c r="I16" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J16" t="n">
         <v>81.40000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.446</v>
+        <v>0.445</v>
       </c>
       <c r="L16" t="n">
         <v>4.6</v>
@@ -3239,31 +3306,31 @@
         <v>13.4</v>
       </c>
       <c r="N16" t="n">
-        <v>0.345</v>
+        <v>0.347</v>
       </c>
       <c r="O16" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="P16" t="n">
         <v>21.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.776</v>
+        <v>0.778</v>
       </c>
       <c r="R16" t="n">
         <v>12.8</v>
       </c>
       <c r="S16" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="T16" t="n">
         <v>42.4</v>
       </c>
       <c r="U16" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V16" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="W16" t="n">
         <v>8.6</v>
@@ -3284,13 +3351,13 @@
         <v>93.59999999999999</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AD16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF16" t="n">
         <v>5</v>
@@ -3302,7 +3369,7 @@
         <v>17</v>
       </c>
       <c r="AI16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ16" t="n">
         <v>17</v>
@@ -3320,19 +3387,19 @@
         <v>23</v>
       </c>
       <c r="AO16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ16" t="n">
         <v>7</v>
       </c>
       <c r="AR16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT16" t="n">
         <v>12</v>
@@ -3341,7 +3408,7 @@
         <v>24</v>
       </c>
       <c r="AV16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AW16" t="n">
         <v>4</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-9-2012-13</t>
+          <t>2013-04-09</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E17" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F17" t="n">
         <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>0.792</v>
+        <v>0.789</v>
       </c>
       <c r="H17" t="n">
         <v>48.5</v>
@@ -3409,37 +3476,37 @@
         <v>38.5</v>
       </c>
       <c r="J17" t="n">
-        <v>77.8</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.495</v>
+        <v>0.496</v>
       </c>
       <c r="L17" t="n">
         <v>8.5</v>
       </c>
       <c r="M17" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0.393</v>
+        <v>0.397</v>
       </c>
       <c r="O17" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="P17" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.761</v>
+        <v>0.76</v>
       </c>
       <c r="R17" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S17" t="n">
         <v>30.1</v>
       </c>
       <c r="T17" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="U17" t="n">
         <v>22.9</v>
@@ -3451,10 +3518,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="X17" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Z17" t="n">
         <v>18.7</v>
@@ -3463,13 +3530,13 @@
         <v>20.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>102.8</v>
+        <v>102.9</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3496,13 +3563,13 @@
         <v>5</v>
       </c>
       <c r="AM17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AN17" t="n">
         <v>2</v>
       </c>
       <c r="AO17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP17" t="n">
         <v>12</v>
@@ -3514,16 +3581,16 @@
         <v>28</v>
       </c>
       <c r="AS17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT17" t="n">
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW17" t="n">
         <v>3</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-9-2012-13</t>
+          <t>2013-04-09</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E18" t="n">
         <v>37</v>
       </c>
       <c r="F18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G18" t="n">
-        <v>0.481</v>
+        <v>0.487</v>
       </c>
       <c r="H18" t="n">
         <v>48.3</v>
@@ -3591,7 +3658,7 @@
         <v>38.2</v>
       </c>
       <c r="J18" t="n">
-        <v>87.40000000000001</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="K18" t="n">
         <v>0.437</v>
@@ -3600,64 +3667,64 @@
         <v>7.1</v>
       </c>
       <c r="M18" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="N18" t="n">
         <v>0.359</v>
       </c>
       <c r="O18" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="P18" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.74</v>
+        <v>0.741</v>
       </c>
       <c r="R18" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="S18" t="n">
         <v>30.8</v>
       </c>
       <c r="T18" t="n">
-        <v>43.7</v>
+        <v>43.8</v>
       </c>
       <c r="U18" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="V18" t="n">
         <v>14.1</v>
       </c>
       <c r="W18" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X18" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="Y18" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>98.8</v>
+        <v>99</v>
       </c>
       <c r="AC18" t="n">
-        <v>-1.3</v>
+        <v>-1.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="AE18" t="n">
         <v>18</v>
       </c>
       <c r="AF18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG18" t="n">
         <v>18</v>
@@ -3666,7 +3733,7 @@
         <v>15</v>
       </c>
       <c r="AI18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ18" t="n">
         <v>1</v>
@@ -3702,13 +3769,13 @@
         <v>5</v>
       </c>
       <c r="AU18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW18" t="n">
         <v>9</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>8</v>
       </c>
       <c r="AX18" t="n">
         <v>2</v>
@@ -3720,7 +3787,7 @@
         <v>9</v>
       </c>
       <c r="BA18" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BB18" t="n">
         <v>12</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-9-2012-13</t>
+          <t>2013-04-09</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E19" t="n">
         <v>29</v>
       </c>
       <c r="F19" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G19" t="n">
-        <v>0.377</v>
+        <v>0.382</v>
       </c>
       <c r="H19" t="n">
         <v>48.1</v>
@@ -3773,10 +3840,10 @@
         <v>35.8</v>
       </c>
       <c r="J19" t="n">
-        <v>81.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="K19" t="n">
-        <v>0.439</v>
+        <v>0.44</v>
       </c>
       <c r="L19" t="n">
         <v>5.4</v>
@@ -3785,7 +3852,7 @@
         <v>17.8</v>
       </c>
       <c r="N19" t="n">
-        <v>0.304</v>
+        <v>0.303</v>
       </c>
       <c r="O19" t="n">
         <v>18.6</v>
@@ -3800,16 +3867,16 @@
         <v>12.1</v>
       </c>
       <c r="S19" t="n">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="T19" t="n">
         <v>42.3</v>
       </c>
       <c r="U19" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="V19" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W19" t="n">
         <v>8.4</v>
@@ -3821,28 +3888,28 @@
         <v>6</v>
       </c>
       <c r="Z19" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="AA19" t="n">
         <v>22.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>95.59999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2.3</v>
+        <v>-2.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="AE19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF19" t="n">
         <v>21</v>
       </c>
       <c r="AG19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH19" t="n">
         <v>26</v>
@@ -3851,7 +3918,7 @@
         <v>25</v>
       </c>
       <c r="AJ19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK19" t="n">
         <v>24</v>
@@ -3884,13 +3951,13 @@
         <v>13</v>
       </c>
       <c r="AU19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX19" t="n">
         <v>18</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-9-2012-13</t>
+          <t>2013-04-09</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E20" t="n">
         <v>27</v>
       </c>
       <c r="F20" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G20" t="n">
-        <v>0.346</v>
+        <v>0.351</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
@@ -3958,16 +4025,16 @@
         <v>80.2</v>
       </c>
       <c r="K20" t="n">
-        <v>0.45</v>
+        <v>0.451</v>
       </c>
       <c r="L20" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="M20" t="n">
         <v>18</v>
       </c>
       <c r="N20" t="n">
-        <v>0.363</v>
+        <v>0.365</v>
       </c>
       <c r="O20" t="n">
         <v>15.2</v>
@@ -3976,7 +4043,7 @@
         <v>19.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.781</v>
+        <v>0.779</v>
       </c>
       <c r="R20" t="n">
         <v>11.7</v>
@@ -3985,7 +4052,7 @@
         <v>29.6</v>
       </c>
       <c r="T20" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="U20" t="n">
         <v>21.1</v>
@@ -4003,7 +4070,7 @@
         <v>6</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AA20" t="n">
         <v>18.5</v>
@@ -4012,25 +4079,25 @@
         <v>94</v>
       </c>
       <c r="AC20" t="n">
-        <v>-3.5</v>
+        <v>-3.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE20" t="n">
         <v>24</v>
       </c>
       <c r="AF20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH20" t="n">
         <v>22</v>
       </c>
       <c r="AI20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ20" t="n">
         <v>26</v>
@@ -4045,7 +4112,7 @@
         <v>21</v>
       </c>
       <c r="AN20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO20" t="n">
         <v>26</v>
@@ -4060,10 +4127,10 @@
         <v>11</v>
       </c>
       <c r="AS20" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AT20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU20" t="n">
         <v>23</v>
@@ -4090,7 +4157,7 @@
         <v>25</v>
       </c>
       <c r="BC20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-9-2012-13</t>
+          <t>2013-04-09</t>
         </is>
       </c>
     </row>
@@ -4119,49 +4186,49 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E21" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F21" t="n">
         <v>26</v>
       </c>
       <c r="G21" t="n">
-        <v>0.662</v>
+        <v>0.658</v>
       </c>
       <c r="H21" t="n">
         <v>48.1</v>
       </c>
       <c r="I21" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="J21" t="n">
         <v>81.2</v>
       </c>
       <c r="K21" t="n">
-        <v>0.449</v>
+        <v>0.447</v>
       </c>
       <c r="L21" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="M21" t="n">
         <v>28.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0.377</v>
+        <v>0.374</v>
       </c>
       <c r="O21" t="n">
         <v>16.3</v>
       </c>
       <c r="P21" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="Q21" t="n">
         <v>0.759</v>
       </c>
       <c r="R21" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S21" t="n">
         <v>29.6</v>
@@ -4170,13 +4237,13 @@
         <v>40.6</v>
       </c>
       <c r="U21" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="V21" t="n">
         <v>12.1</v>
       </c>
       <c r="W21" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X21" t="n">
         <v>3.6</v>
@@ -4185,28 +4252,28 @@
         <v>4</v>
       </c>
       <c r="Z21" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AA21" t="n">
         <v>19.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="AE21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF21" t="n">
         <v>6</v>
       </c>
       <c r="AG21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH21" t="n">
         <v>30</v>
@@ -4218,19 +4285,19 @@
         <v>19</v>
       </c>
       <c r="AK21" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
       </c>
       <c r="AM21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AP21" t="n">
         <v>16</v>
@@ -4242,7 +4309,7 @@
         <v>18</v>
       </c>
       <c r="AS21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT21" t="n">
         <v>25</v>
@@ -4263,13 +4330,13 @@
         <v>2</v>
       </c>
       <c r="AZ21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA21" t="n">
         <v>19</v>
       </c>
       <c r="BB21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC21" t="n">
         <v>7</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-9-2012-13</t>
+          <t>2013-04-09</t>
         </is>
       </c>
     </row>
@@ -4301,49 +4368,49 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E22" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F22" t="n">
         <v>21</v>
       </c>
       <c r="G22" t="n">
-        <v>0.731</v>
+        <v>0.727</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
       </c>
       <c r="I22" t="n">
-        <v>38</v>
+        <v>38.1</v>
       </c>
       <c r="J22" t="n">
         <v>79</v>
       </c>
       <c r="K22" t="n">
-        <v>0.481</v>
+        <v>0.482</v>
       </c>
       <c r="L22" t="n">
         <v>7.3</v>
       </c>
       <c r="M22" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="N22" t="n">
-        <v>0.381</v>
+        <v>0.38</v>
       </c>
       <c r="O22" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="P22" t="n">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.829</v>
+        <v>0.828</v>
       </c>
       <c r="R22" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="S22" t="n">
         <v>33.2</v>
@@ -4355,7 +4422,7 @@
         <v>21.4</v>
       </c>
       <c r="V22" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W22" t="n">
         <v>8.199999999999999</v>
@@ -4373,16 +4440,16 @@
         <v>21</v>
       </c>
       <c r="AB22" t="n">
-        <v>105.8</v>
+        <v>106</v>
       </c>
       <c r="AC22" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF22" t="n">
         <v>3</v>
@@ -4391,7 +4458,7 @@
         <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI22" t="n">
         <v>8</v>
@@ -4424,7 +4491,7 @@
         <v>25</v>
       </c>
       <c r="AS22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT22" t="n">
         <v>6</v>
@@ -4448,10 +4515,10 @@
         <v>18</v>
       </c>
       <c r="BA22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-9-2012-13</t>
+          <t>2013-04-09</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-6.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4573,7 +4640,7 @@
         <v>29</v>
       </c>
       <c r="AH23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI23" t="n">
         <v>10</v>
@@ -4582,7 +4649,7 @@
         <v>4</v>
       </c>
       <c r="AK23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL23" t="n">
         <v>21</v>
@@ -4603,7 +4670,7 @@
         <v>12</v>
       </c>
       <c r="AR23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS23" t="n">
         <v>9</v>
@@ -4612,7 +4679,7 @@
         <v>11</v>
       </c>
       <c r="AU23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV23" t="n">
         <v>11</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-9-2012-13</t>
+          <t>2013-04-09</t>
         </is>
       </c>
     </row>
@@ -4665,70 +4732,70 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E24" t="n">
         <v>31</v>
       </c>
       <c r="F24" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G24" t="n">
-        <v>0.403</v>
+        <v>0.408</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
       </c>
       <c r="I24" t="n">
-        <v>37.2</v>
+        <v>37.3</v>
       </c>
       <c r="J24" t="n">
-        <v>83.8</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
       <c r="L24" t="n">
         <v>6.3</v>
       </c>
       <c r="M24" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0.362</v>
+        <v>0.36</v>
       </c>
       <c r="O24" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="P24" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.723</v>
+        <v>0.722</v>
       </c>
       <c r="R24" t="n">
         <v>10.9</v>
       </c>
       <c r="S24" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="T24" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="U24" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="V24" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="W24" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X24" t="n">
         <v>4.7</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z24" t="n">
         <v>18.5</v>
@@ -4737,13 +4804,13 @@
         <v>16.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>92.8</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="AC24" t="n">
-        <v>-3.6</v>
+        <v>-3.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="AE24" t="n">
         <v>20</v>
@@ -4758,13 +4825,13 @@
         <v>23</v>
       </c>
       <c r="AI24" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AJ24" t="n">
         <v>7</v>
       </c>
       <c r="AK24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL24" t="n">
         <v>22</v>
@@ -4773,7 +4840,7 @@
         <v>25</v>
       </c>
       <c r="AN24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4785,16 +4852,16 @@
         <v>25</v>
       </c>
       <c r="AR24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS24" t="n">
         <v>15</v>
       </c>
       <c r="AT24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV24" t="n">
         <v>2</v>
@@ -4806,7 +4873,7 @@
         <v>20</v>
       </c>
       <c r="AY24" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ24" t="n">
         <v>5</v>
@@ -4818,7 +4885,7 @@
         <v>29</v>
       </c>
       <c r="BC24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-9-2012-13</t>
+          <t>2013-04-09</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E25" t="n">
         <v>23</v>
       </c>
       <c r="F25" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G25" t="n">
-        <v>0.295</v>
+        <v>0.299</v>
       </c>
       <c r="H25" t="n">
         <v>48.3</v>
@@ -4865,7 +4932,7 @@
         <v>37.2</v>
       </c>
       <c r="J25" t="n">
-        <v>84.09999999999999</v>
+        <v>84</v>
       </c>
       <c r="K25" t="n">
         <v>0.442</v>
@@ -4874,10 +4941,10 @@
         <v>5.7</v>
       </c>
       <c r="M25" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0.327</v>
+        <v>0.325</v>
       </c>
       <c r="O25" t="n">
         <v>14.7</v>
@@ -4886,7 +4953,7 @@
         <v>19.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.742</v>
+        <v>0.741</v>
       </c>
       <c r="R25" t="n">
         <v>11.7</v>
@@ -4898,10 +4965,10 @@
         <v>41.5</v>
       </c>
       <c r="U25" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="V25" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="W25" t="n">
         <v>8</v>
@@ -4916,16 +4983,16 @@
         <v>20.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>94.8</v>
+        <v>94.7</v>
       </c>
       <c r="AC25" t="n">
-        <v>-6.6</v>
+        <v>-6.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE25" t="n">
         <v>28</v>
@@ -4940,7 +5007,7 @@
         <v>17</v>
       </c>
       <c r="AI25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ25" t="n">
         <v>5</v>
@@ -4949,7 +5016,7 @@
         <v>23</v>
       </c>
       <c r="AL25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM25" t="n">
         <v>24</v>
@@ -4967,31 +5034,31 @@
         <v>20</v>
       </c>
       <c r="AR25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT25" t="n">
         <v>17</v>
       </c>
       <c r="AU25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV25" t="n">
         <v>29</v>
       </c>
       <c r="AW25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY25" t="n">
         <v>17</v>
       </c>
       <c r="AZ25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA25" t="n">
         <v>27</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-9-2012-13</t>
+          <t>2013-04-09</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-2.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="AE26" t="n">
         <v>19</v>
@@ -5119,7 +5186,7 @@
         <v>19</v>
       </c>
       <c r="AH26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI26" t="n">
         <v>18</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-9-2012-13</t>
+          <t>2013-04-09</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-4.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="AE27" t="n">
         <v>24</v>
@@ -5319,7 +5386,7 @@
         <v>11</v>
       </c>
       <c r="AN27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO27" t="n">
         <v>7</v>
@@ -5337,10 +5404,10 @@
         <v>28</v>
       </c>
       <c r="AT27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV27" t="n">
         <v>17</v>
@@ -5361,7 +5428,7 @@
         <v>12</v>
       </c>
       <c r="BB27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC27" t="n">
         <v>27</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-9-2012-13</t>
+          <t>2013-04-09</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>7.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
@@ -5483,13 +5550,13 @@
         <v>2</v>
       </c>
       <c r="AH28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI28" t="n">
         <v>2</v>
       </c>
       <c r="AJ28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
@@ -5498,7 +5565,7 @@
         <v>6</v>
       </c>
       <c r="AM28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN28" t="n">
         <v>4</v>
@@ -5528,7 +5595,7 @@
         <v>16</v>
       </c>
       <c r="AW28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX28" t="n">
         <v>10</v>
@@ -5540,7 +5607,7 @@
         <v>1</v>
       </c>
       <c r="BA28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB28" t="n">
         <v>4</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-9-2012-13</t>
+          <t>2013-04-09</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E29" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F29" t="n">
         <v>48</v>
       </c>
       <c r="G29" t="n">
-        <v>0.385</v>
+        <v>0.377</v>
       </c>
       <c r="H29" t="n">
         <v>48.8</v>
@@ -5593,52 +5660,52 @@
         <v>36.3</v>
       </c>
       <c r="J29" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="K29" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L29" t="n">
         <v>6.9</v>
       </c>
       <c r="M29" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="N29" t="n">
         <v>0.339</v>
       </c>
       <c r="O29" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="P29" t="n">
         <v>22.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.787</v>
+        <v>0.786</v>
       </c>
       <c r="R29" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S29" t="n">
         <v>29.3</v>
       </c>
       <c r="T29" t="n">
-        <v>40</v>
+        <v>40.1</v>
       </c>
       <c r="U29" t="n">
         <v>21.5</v>
       </c>
       <c r="V29" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="W29" t="n">
         <v>7.3</v>
       </c>
       <c r="X29" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y29" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z29" t="n">
         <v>22.7</v>
@@ -5653,16 +5720,16 @@
         <v>-2.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE29" t="n">
         <v>21</v>
       </c>
       <c r="AF29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH29" t="n">
         <v>2</v>
@@ -5671,10 +5738,10 @@
         <v>21</v>
       </c>
       <c r="AJ29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL29" t="n">
         <v>15</v>
@@ -5686,7 +5753,7 @@
         <v>26</v>
       </c>
       <c r="AO29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP29" t="n">
         <v>15</v>
@@ -5695,7 +5762,7 @@
         <v>5</v>
       </c>
       <c r="AR29" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AS29" t="n">
         <v>27</v>
@@ -5707,7 +5774,7 @@
         <v>20</v>
       </c>
       <c r="AV29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW29" t="n">
         <v>19</v>
@@ -5716,7 +5783,7 @@
         <v>19</v>
       </c>
       <c r="AY29" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AZ29" t="n">
         <v>30</v>
@@ -5728,7 +5795,7 @@
         <v>16</v>
       </c>
       <c r="BC29" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-9-2012-13</t>
+          <t>2013-04-09</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E30" t="n">
         <v>41</v>
       </c>
       <c r="F30" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G30" t="n">
-        <v>0.519</v>
+        <v>0.526</v>
       </c>
       <c r="H30" t="n">
         <v>48.5</v>
@@ -5778,34 +5845,34 @@
         <v>82.09999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>0.454</v>
+        <v>0.455</v>
       </c>
       <c r="L30" t="n">
         <v>6.2</v>
       </c>
       <c r="M30" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="N30" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="O30" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="P30" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="Q30" t="n">
         <v>0.763</v>
       </c>
       <c r="R30" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="S30" t="n">
-        <v>29.9</v>
+        <v>29.8</v>
       </c>
       <c r="T30" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U30" t="n">
         <v>22.8</v>
@@ -5817,7 +5884,7 @@
         <v>8.4</v>
       </c>
       <c r="X30" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="Y30" t="n">
         <v>5.9</v>
@@ -5829,10 +5896,10 @@
         <v>20.4</v>
       </c>
       <c r="AB30" t="n">
-        <v>98.3</v>
+        <v>98.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="AD30" t="n">
         <v>1</v>
@@ -5841,10 +5908,10 @@
         <v>14</v>
       </c>
       <c r="AF30" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG30" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH30" t="n">
         <v>7</v>
@@ -5862,13 +5929,13 @@
         <v>24</v>
       </c>
       <c r="AM30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AN30" t="n">
         <v>9</v>
       </c>
       <c r="AO30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP30" t="n">
         <v>10</v>
@@ -5877,22 +5944,22 @@
         <v>13</v>
       </c>
       <c r="AR30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT30" t="n">
         <v>15</v>
       </c>
       <c r="AU30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX30" t="n">
         <v>5</v>
@@ -5910,7 +5977,7 @@
         <v>13</v>
       </c>
       <c r="BC30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-9-2012-13</t>
+          <t>2013-04-09</t>
         </is>
       </c>
     </row>
@@ -5939,19 +6006,19 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E31" t="n">
         <v>29</v>
       </c>
       <c r="F31" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G31" t="n">
-        <v>0.372</v>
+        <v>0.377</v>
       </c>
       <c r="H31" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I31" t="n">
         <v>35.4</v>
@@ -5966,16 +6033,16 @@
         <v>6.7</v>
       </c>
       <c r="M31" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="N31" t="n">
-        <v>0.365</v>
+        <v>0.364</v>
       </c>
       <c r="O31" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="P31" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="Q31" t="n">
         <v>0.734</v>
@@ -5984,13 +6051,13 @@
         <v>10.9</v>
       </c>
       <c r="S31" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="T31" t="n">
-        <v>43.3</v>
+        <v>43.4</v>
       </c>
       <c r="U31" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="V31" t="n">
         <v>15.1</v>
@@ -5999,43 +6066,43 @@
         <v>7.2</v>
       </c>
       <c r="X31" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y31" t="n">
         <v>4.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>93.2</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>-2.4</v>
+        <v>-2.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE31" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF31" t="n">
         <v>22</v>
       </c>
-      <c r="AF31" t="n">
-        <v>23</v>
-      </c>
       <c r="AG31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI31" t="n">
         <v>28</v>
       </c>
       <c r="AJ31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK31" t="n">
         <v>28</v>
@@ -6047,10 +6114,10 @@
         <v>20</v>
       </c>
       <c r="AN31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP31" t="n">
         <v>18</v>
@@ -6071,7 +6138,7 @@
         <v>19</v>
       </c>
       <c r="AV31" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AW31" t="n">
         <v>22</v>
@@ -6083,16 +6150,16 @@
         <v>8</v>
       </c>
       <c r="AZ31" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA31" t="n">
         <v>23</v>
       </c>
       <c r="BB31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC31" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-9-2012-13</t>
+          <t>2013-04-09</t>
         </is>
       </c>
     </row>
